--- a/data_management2026/database_entry.xlsx
+++ b/data_management2026/database_entry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/estherchen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tippi\SynologyDrive\Tsing_Hua\third_grade\project\RealTimeAccompaniment_COPY\data_management2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D4D49D-4F30-E343-88E8-E4A2A180AD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856A94D4-D7E0-4E24-90DE-16677F8E4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="4515" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="712">
   <si>
     <t>entry</t>
   </si>
@@ -2104,41 +2104,6 @@
     <t>202412 Experiments\20241217\Recordings Edit 4.tracktionedit</t>
   </si>
   <si>
-    <t>202412 Experiments\20241217\Recordings Edit 5.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241218\asdf Edit 1.tracktionedit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>202412 Experiments\20241218\asdf Edit 2.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241218\asdf Edit 3.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241218\asdf Edit 4.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 2.tracktionedit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 3.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 4.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 5.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 6.tracktionedit</t>
-  </si>
-  <si>
-    <t>202412 Experiments\20241220\Edit 7.tracktionedit</t>
-  </si>
-  <si>
     <t>曹若忻or游幸璇</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2197,13 +2162,52 @@
   <si>
     <t>data_management2026\py_scripts_and_notes\extract_interpretation_Heidenroslein.py</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_2_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_2_Human_2.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_4_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_4_Human_2.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_2_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_2_Human_2.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_4_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_4_Human_2.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_4hands.py</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_5hands.py</t>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_6hands.py</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2606,22 +2610,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K325"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K329"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.78515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.78515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.78515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2656,7 +2660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2688,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2720,7 +2724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2752,7 +2756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2784,7 +2788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2816,7 +2820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2848,7 +2852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2880,7 +2884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2912,7 +2916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2944,7 +2948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2976,7 +2980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3008,7 +3012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3040,7 +3044,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1">
+    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3072,7 +3076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1">
+    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3104,7 +3108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1">
+    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3136,7 +3140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="18.75" customHeight="1">
+    <row r="17" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3168,7 +3172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="18.75" customHeight="1">
+    <row r="18" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3200,7 +3204,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="18.75" customHeight="1">
+    <row r="19" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3232,7 +3236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="18.75" customHeight="1">
+    <row r="20" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="18.75" customHeight="1">
+    <row r="21" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3296,7 +3300,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="18.75" customHeight="1">
+    <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3328,7 +3332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="18.75" customHeight="1">
+    <row r="23" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3360,7 +3364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="18.75" customHeight="1">
+    <row r="24" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3392,7 +3396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="18.75" customHeight="1">
+    <row r="25" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3424,7 +3428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="18.75" customHeight="1">
+    <row r="26" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3456,7 +3460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="18.75" customHeight="1">
+    <row r="27" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3488,7 +3492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18.75" customHeight="1">
+    <row r="28" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3520,7 +3524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18.75" customHeight="1">
+    <row r="29" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3552,7 +3556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="18.75" customHeight="1">
+    <row r="30" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3584,7 +3588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="18.75" customHeight="1">
+    <row r="31" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3616,7 +3620,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="18.75" customHeight="1">
+    <row r="32" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3648,7 +3652,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="18.75" customHeight="1">
+    <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3680,7 +3684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18.75" customHeight="1">
+    <row r="34" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3712,7 +3716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="18.75" customHeight="1">
+    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3744,7 +3748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="18.75" customHeight="1">
+    <row r="36" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3776,7 +3780,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="18.75" customHeight="1">
+    <row r="37" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3808,7 +3812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="18.75" customHeight="1">
+    <row r="38" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3840,7 +3844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="18.75" customHeight="1">
+    <row r="39" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3872,7 +3876,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="18.75" customHeight="1">
+    <row r="40" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="18.75" customHeight="1">
+    <row r="41" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3936,7 +3940,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="18.75" customHeight="1">
+    <row r="42" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3968,7 +3972,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="18.75" customHeight="1">
+    <row r="43" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18.75" customHeight="1">
+    <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4032,7 +4036,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18.75" customHeight="1">
+    <row r="45" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4064,7 +4068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18.75" customHeight="1">
+    <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4096,7 +4100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="18.75" customHeight="1">
+    <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4128,7 +4132,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="18.75" customHeight="1">
+    <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4160,7 +4164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="18.75" customHeight="1">
+    <row r="49" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4192,7 +4196,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="18.75" customHeight="1">
+    <row r="50" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4224,7 +4228,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="18.75" customHeight="1">
+    <row r="51" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4256,7 +4260,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="18.75" customHeight="1">
+    <row r="52" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -4288,7 +4292,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="18.75" customHeight="1">
+    <row r="53" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4320,7 +4324,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="18.75" customHeight="1">
+    <row r="54" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4352,7 +4356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="18.75" customHeight="1">
+    <row r="55" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4384,7 +4388,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="18.75" customHeight="1">
+    <row r="56" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4416,7 +4420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="18.75" customHeight="1">
+    <row r="57" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4448,7 +4452,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="18.75" customHeight="1">
+    <row r="58" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4480,7 +4484,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="18.75" customHeight="1">
+    <row r="59" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4512,7 +4516,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="18.75" customHeight="1">
+    <row r="60" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4544,7 +4548,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="18.75" customHeight="1">
+    <row r="61" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4576,7 +4580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="18.75" customHeight="1">
+    <row r="62" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4608,7 +4612,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="18.75" customHeight="1">
+    <row r="63" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4640,7 +4644,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="18.75" customHeight="1">
+    <row r="64" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -4672,7 +4676,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="18.75" customHeight="1">
+    <row r="65" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -4704,7 +4708,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="18.75" customHeight="1">
+    <row r="66" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -4736,7 +4740,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="18.75" customHeight="1">
+    <row r="67" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4768,7 +4772,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="18.75" customHeight="1">
+    <row r="68" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4800,7 +4804,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="18.75" customHeight="1">
+    <row r="69" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="18.75" customHeight="1">
+    <row r="70" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="18.75" customHeight="1">
+    <row r="71" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4896,7 +4900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="18.75" customHeight="1">
+    <row r="72" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="18.75" customHeight="1">
+    <row r="73" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4960,7 +4964,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="18.75" customHeight="1">
+    <row r="74" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4992,7 +4996,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="18.75" customHeight="1">
+    <row r="75" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -5024,7 +5028,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="18.75" customHeight="1">
+    <row r="76" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -5056,7 +5060,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="18.75" customHeight="1">
+    <row r="77" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -5088,7 +5092,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="18.75" customHeight="1">
+    <row r="78" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -5120,7 +5124,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="18.75" customHeight="1">
+    <row r="79" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -5152,7 +5156,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="18.75" customHeight="1">
+    <row r="80" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -5184,7 +5188,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="18.75" customHeight="1">
+    <row r="81" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -5216,7 +5220,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="18.75" customHeight="1">
+    <row r="82" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -5248,7 +5252,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="18.75" customHeight="1">
+    <row r="83" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -5280,7 +5284,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="18.75" customHeight="1">
+    <row r="84" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -5312,7 +5316,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="18.75" customHeight="1">
+    <row r="85" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -5344,7 +5348,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="18.75" customHeight="1">
+    <row r="86" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -5376,7 +5380,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="18.75" customHeight="1">
+    <row r="87" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -5408,7 +5412,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="18.75" customHeight="1">
+    <row r="88" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -5440,7 +5444,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="18.75" customHeight="1">
+    <row r="89" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="18.75" customHeight="1">
+    <row r="90" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -5504,7 +5508,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="18.75" customHeight="1">
+    <row r="91" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -5536,7 +5540,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="18.75" customHeight="1">
+    <row r="92" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -5568,7 +5572,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="18.75" customHeight="1">
+    <row r="93" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -5600,7 +5604,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="18.75" customHeight="1">
+    <row r="94" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -5632,7 +5636,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="18.75" customHeight="1">
+    <row r="95" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -5664,7 +5668,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="18.75" customHeight="1">
+    <row r="96" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -5696,7 +5700,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="18.75" customHeight="1">
+    <row r="97" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -5728,7 +5732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="18.75" customHeight="1">
+    <row r="98" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -5760,7 +5764,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="18.75" customHeight="1">
+    <row r="99" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -5792,7 +5796,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="18.75" customHeight="1">
+    <row r="100" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -5824,7 +5828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="18.75" customHeight="1">
+    <row r="101" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5856,7 +5860,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18.75" customHeight="1">
+    <row r="102" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -5888,7 +5892,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="18.75" customHeight="1">
+    <row r="103" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5920,7 +5924,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="18.75" customHeight="1">
+    <row r="104" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -5952,7 +5956,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="18.75" customHeight="1">
+    <row r="105" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -5984,7 +5988,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="18.75" customHeight="1">
+    <row r="106" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -6016,7 +6020,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="18.75" customHeight="1">
+    <row r="107" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -6048,7 +6052,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="18.75" customHeight="1">
+    <row r="108" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -6080,7 +6084,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="18.75" customHeight="1">
+    <row r="109" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -6112,7 +6116,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="18.75" customHeight="1">
+    <row r="110" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -6144,7 +6148,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="18.75" customHeight="1">
+    <row r="111" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -6176,7 +6180,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="18.75" customHeight="1">
+    <row r="112" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -6208,7 +6212,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="18.75" customHeight="1">
+    <row r="113" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -6240,7 +6244,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="18.75" customHeight="1">
+    <row r="114" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -6272,7 +6276,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="18.75" customHeight="1">
+    <row r="115" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -6304,7 +6308,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="18.75" customHeight="1">
+    <row r="116" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -6336,7 +6340,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="18.75" customHeight="1">
+    <row r="117" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -6368,7 +6372,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="18.75" customHeight="1">
+    <row r="118" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -6400,7 +6404,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="18.75" customHeight="1">
+    <row r="119" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -6432,7 +6436,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="18.75" customHeight="1">
+    <row r="120" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -6464,7 +6468,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="18.75" customHeight="1">
+    <row r="121" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -6496,7 +6500,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="18.75" customHeight="1">
+    <row r="122" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -6528,7 +6532,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="18.75" customHeight="1">
+    <row r="123" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -6560,7 +6564,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="18.75" customHeight="1">
+    <row r="124" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -6592,7 +6596,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="18.75" customHeight="1">
+    <row r="125" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -6624,7 +6628,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1">
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -6656,7 +6660,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="18.75" customHeight="1">
+    <row r="127" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -6688,7 +6692,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="18.75" customHeight="1">
+    <row r="128" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -6720,7 +6724,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="18.75" customHeight="1">
+    <row r="129" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -6752,7 +6756,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="18.75" customHeight="1">
+    <row r="130" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -6784,7 +6788,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="18.75" customHeight="1">
+    <row r="131" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -6816,7 +6820,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="18.75" customHeight="1">
+    <row r="132" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -6848,7 +6852,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="18.75" customHeight="1">
+    <row r="133" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6880,7 +6884,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="18.75" customHeight="1">
+    <row r="134" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="18.75" customHeight="1">
+    <row r="135" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="18.75" customHeight="1">
+    <row r="136" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -6976,7 +6980,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="18.75" customHeight="1">
+    <row r="137" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -7008,7 +7012,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="18.75" customHeight="1">
+    <row r="138" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -7040,7 +7044,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="18.75" customHeight="1">
+    <row r="139" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -7072,7 +7076,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="18.75" customHeight="1">
+    <row r="140" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -7104,7 +7108,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="18.75" customHeight="1">
+    <row r="141" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -7136,7 +7140,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="18.75" customHeight="1">
+    <row r="142" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -7168,7 +7172,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="18.75" customHeight="1">
+    <row r="143" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -7200,7 +7204,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="18.75" customHeight="1">
+    <row r="144" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -7232,7 +7236,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="18.75" customHeight="1">
+    <row r="145" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -7264,7 +7268,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="18.75" customHeight="1">
+    <row r="146" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -7296,7 +7300,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="18.75" customHeight="1">
+    <row r="147" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -7328,7 +7332,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="18.75" customHeight="1">
+    <row r="148" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -7360,7 +7364,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="18.75" customHeight="1">
+    <row r="149" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -7392,7 +7396,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="18.75" customHeight="1">
+    <row r="150" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -7424,7 +7428,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="18.75" customHeight="1">
+    <row r="151" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -7456,7 +7460,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="18.75" customHeight="1">
+    <row r="152" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -7488,7 +7492,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="18.75" customHeight="1">
+    <row r="153" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -7520,7 +7524,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="18.75" customHeight="1">
+    <row r="154" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -7552,7 +7556,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="18.75" customHeight="1">
+    <row r="155" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -7584,7 +7588,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="18.75" customHeight="1">
+    <row r="156" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -7616,7 +7620,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="18.75" customHeight="1">
+    <row r="157" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -7648,7 +7652,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="18.75" customHeight="1">
+    <row r="158" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="18.75" customHeight="1">
+    <row r="159" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -7712,7 +7716,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="18.75" customHeight="1">
+    <row r="160" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -7744,7 +7748,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="18.75" customHeight="1">
+    <row r="161" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -7776,7 +7780,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="18.75" customHeight="1">
+    <row r="162" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -7808,7 +7812,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="18.75" customHeight="1">
+    <row r="163" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -7840,7 +7844,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="18.75" customHeight="1">
+    <row r="164" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -7872,7 +7876,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="18.75" customHeight="1">
+    <row r="165" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -7904,7 +7908,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="18.75" customHeight="1">
+    <row r="166" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -7936,7 +7940,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="18.75" customHeight="1">
+    <row r="167" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -7968,7 +7972,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="18.75" customHeight="1">
+    <row r="168" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -8000,7 +8004,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="18.75" customHeight="1">
+    <row r="169" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -8032,7 +8036,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="18.75" customHeight="1">
+    <row r="170" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -8064,7 +8068,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="18.75" customHeight="1">
+    <row r="171" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="18.75" customHeight="1">
+    <row r="172" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -8128,7 +8132,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="18.75" customHeight="1">
+    <row r="173" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -8160,7 +8164,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="18.75" customHeight="1">
+    <row r="174" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -8192,7 +8196,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="18.75" customHeight="1">
+    <row r="175" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -8224,7 +8228,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="18.75" customHeight="1">
+    <row r="176" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -8256,7 +8260,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="19.5" customHeight="1">
+    <row r="177" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -8288,7 +8292,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="20.25" customHeight="1">
+    <row r="178" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -8320,7 +8324,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="19.5" customHeight="1">
+    <row r="179" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -8352,7 +8356,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="20.25" customHeight="1">
+    <row r="180" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -8384,7 +8388,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="19.5" customHeight="1">
+    <row r="181" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="20.25" customHeight="1">
+    <row r="182" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -8448,7 +8452,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="19.5" customHeight="1">
+    <row r="183" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -8480,7 +8484,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="20.25" customHeight="1">
+    <row r="184" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -8512,7 +8516,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="19.5" customHeight="1">
+    <row r="185" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -8544,7 +8548,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="20.25" customHeight="1">
+    <row r="186" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -8576,7 +8580,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="19.5" customHeight="1">
+    <row r="187" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -8608,7 +8612,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="20.25" customHeight="1">
+    <row r="188" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -8640,7 +8644,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="19.5" customHeight="1">
+    <row r="189" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -8672,7 +8676,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="20.25" customHeight="1">
+    <row r="190" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -8704,7 +8708,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="19.5" customHeight="1">
+    <row r="191" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -8736,7 +8740,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="20.25" customHeight="1">
+    <row r="192" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -8768,7 +8772,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="19.5" customHeight="1">
+    <row r="193" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -8800,7 +8804,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="20.25" customHeight="1">
+    <row r="194" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -8832,7 +8836,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="19.5" customHeight="1">
+    <row r="195" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -8864,7 +8868,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="20.25" customHeight="1">
+    <row r="196" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -8896,7 +8900,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="19.5" customHeight="1">
+    <row r="197" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -8928,7 +8932,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="20.25" customHeight="1">
+    <row r="198" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -8960,7 +8964,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="19.5" customHeight="1">
+    <row r="199" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -8992,7 +8996,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="20.25" customHeight="1">
+    <row r="200" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -9024,7 +9028,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="19.5" customHeight="1">
+    <row r="201" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -9056,7 +9060,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="18.75" customHeight="1">
+    <row r="202" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -9088,7 +9092,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="18.75" customHeight="1">
+    <row r="203" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -9120,7 +9124,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="18.75" customHeight="1">
+    <row r="204" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -9152,7 +9156,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="18.75" customHeight="1">
+    <row r="205" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -9184,7 +9188,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="18.75" customHeight="1">
+    <row r="206" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -9216,7 +9220,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="18.75" customHeight="1">
+    <row r="207" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -9248,7 +9252,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="18.75" customHeight="1">
+    <row r="208" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -9280,7 +9284,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="18.75" customHeight="1">
+    <row r="209" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -9312,7 +9316,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="18.75" customHeight="1">
+    <row r="210" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -9344,7 +9348,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="18.75" customHeight="1">
+    <row r="211" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -9376,7 +9380,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="18.75" customHeight="1">
+    <row r="212" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -9408,7 +9412,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="18.75" customHeight="1">
+    <row r="213" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -9440,7 +9444,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="18.75" customHeight="1">
+    <row r="214" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -9472,7 +9476,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="18.75" customHeight="1">
+    <row r="215" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -9504,7 +9508,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="18.75" customHeight="1">
+    <row r="216" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -9536,7 +9540,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="18.75" customHeight="1">
+    <row r="217" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -9568,7 +9572,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="18.75" customHeight="1">
+    <row r="218" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -9600,7 +9604,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="18.75" customHeight="1">
+    <row r="219" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -9632,7 +9636,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="18.75" customHeight="1">
+    <row r="220" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -9664,7 +9668,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="18.75" customHeight="1">
+    <row r="221" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -9696,7 +9700,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="18.75" customHeight="1">
+    <row r="222" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -9728,7 +9732,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="18.75" customHeight="1">
+    <row r="223" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -9760,7 +9764,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="18.75" customHeight="1">
+    <row r="224" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -9792,7 +9796,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="18.75" customHeight="1">
+    <row r="225" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -9824,7 +9828,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="18.75" customHeight="1">
+    <row r="226" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -9856,7 +9860,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="18.75" customHeight="1">
+    <row r="227" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -9888,7 +9892,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="18.75" customHeight="1">
+    <row r="228" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="18.75" customHeight="1">
+    <row r="229" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -9952,7 +9956,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="18.75" customHeight="1">
+    <row r="230" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -9984,7 +9988,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="18.75" customHeight="1">
+    <row r="231" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -10016,7 +10020,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="18.75" customHeight="1">
+    <row r="232" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -10048,7 +10052,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="18.75" customHeight="1">
+    <row r="233" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -10080,7 +10084,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="18.75" customHeight="1">
+    <row r="234" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -10112,7 +10116,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="18.75" customHeight="1">
+    <row r="235" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -10144,7 +10148,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="18.75" customHeight="1">
+    <row r="236" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -10176,7 +10180,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="18.75" customHeight="1">
+    <row r="237" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -10208,7 +10212,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="18.75" customHeight="1">
+    <row r="238" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -10240,7 +10244,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="18.75" customHeight="1">
+    <row r="239" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -10272,7 +10276,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="18.75" customHeight="1">
+    <row r="240" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -10304,7 +10308,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="18.75" customHeight="1">
+    <row r="241" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -10336,7 +10340,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="18.75" customHeight="1">
+    <row r="242" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -10368,7 +10372,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="18.75" customHeight="1">
+    <row r="243" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -10400,7 +10404,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="18.75" customHeight="1">
+    <row r="244" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -10432,7 +10436,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="18.75" customHeight="1">
+    <row r="245" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -10464,7 +10468,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="18.75" customHeight="1">
+    <row r="246" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -10496,7 +10500,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="18.75" customHeight="1">
+    <row r="247" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -10528,7 +10532,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="18.75" customHeight="1">
+    <row r="248" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -10563,7 +10567,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="18.75" customHeight="1">
+    <row r="249" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -10598,7 +10602,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="18.75" customHeight="1">
+    <row r="250" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -10633,7 +10637,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="18.75" customHeight="1">
+    <row r="251" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -10668,7 +10672,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="18.75" customHeight="1">
+    <row r="252" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -10703,7 +10707,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="18.75" customHeight="1">
+    <row r="253" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -10738,7 +10742,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="18.75" customHeight="1">
+    <row r="254" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -10773,7 +10777,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="18.75" customHeight="1">
+    <row r="255" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -10808,7 +10812,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="18.75" customHeight="1">
+    <row r="256" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -10843,7 +10847,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="18.75" customHeight="1">
+    <row r="257" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -10878,7 +10882,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="18.75" customHeight="1">
+    <row r="258" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -10913,7 +10917,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="18.75" customHeight="1">
+    <row r="259" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -10948,7 +10952,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="18.75" customHeight="1">
+    <row r="260" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -10983,7 +10987,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="18.75" customHeight="1">
+    <row r="261" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -11018,7 +11022,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="18.75" customHeight="1">
+    <row r="262" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -11053,7 +11057,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="18.75" customHeight="1">
+    <row r="263" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -11088,7 +11092,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="18.75" customHeight="1">
+    <row r="264" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -11123,7 +11127,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="18.75" customHeight="1">
+    <row r="265" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -11158,7 +11162,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="18.75" customHeight="1">
+    <row r="266" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -11193,7 +11197,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="18.75" customHeight="1">
+    <row r="267" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -11228,7 +11232,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="18.75" customHeight="1">
+    <row r="268" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="18.75" customHeight="1">
+    <row r="269" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -11298,7 +11302,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="18.75" customHeight="1">
+    <row r="270" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -11333,7 +11337,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="18.75" customHeight="1">
+    <row r="271" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -11368,7 +11372,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="18.75" customHeight="1">
+    <row r="272" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -11403,7 +11407,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="18.75" customHeight="1">
+    <row r="273" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -11438,7 +11442,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="18.75" customHeight="1">
+    <row r="274" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -11473,7 +11477,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="18.75" customHeight="1">
+    <row r="275" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -11508,7 +11512,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="18.75" customHeight="1">
+    <row r="276" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -11543,7 +11547,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="18.75" customHeight="1">
+    <row r="277" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -11578,7 +11582,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="18.75" customHeight="1">
+    <row r="278" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -11613,7 +11617,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="18.75" customHeight="1">
+    <row r="279" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -11648,7 +11652,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="18.75" customHeight="1">
+    <row r="280" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -11683,7 +11687,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="18.75" customHeight="1">
+    <row r="281" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -11718,7 +11722,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="18.75" customHeight="1">
+    <row r="282" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -11753,7 +11757,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="18.75" customHeight="1">
+    <row r="283" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -11788,7 +11792,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="18.75" customHeight="1">
+    <row r="284" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -11823,7 +11827,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="18.75" customHeight="1">
+    <row r="285" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -11858,7 +11862,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="18.75" customHeight="1">
+    <row r="286" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -11893,7 +11897,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="18.75" customHeight="1">
+    <row r="287" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -11928,7 +11932,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="18.75" customHeight="1">
+    <row r="288" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -11963,7 +11967,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="18.75" customHeight="1">
+    <row r="289" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -11998,7 +12002,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="18.75" customHeight="1">
+    <row r="290" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -12033,7 +12037,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="18.75" customHeight="1">
+    <row r="291" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -12068,7 +12072,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="18.75" customHeight="1">
+    <row r="292" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -12103,7 +12107,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="18.75" customHeight="1">
+    <row r="293" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -12138,7 +12142,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="18.75" customHeight="1">
+    <row r="294" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -12173,7 +12177,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="18.75" customHeight="1">
+    <row r="295" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -12208,7 +12212,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="18.75" customHeight="1">
+    <row r="296" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -12243,7 +12247,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="18.75" customHeight="1">
+    <row r="297" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -12278,7 +12282,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="18.75" customHeight="1">
+    <row r="298" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -12313,7 +12317,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="18.75" customHeight="1">
+    <row r="299" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -12348,7 +12352,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="18.75" customHeight="1">
+    <row r="300" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -12383,7 +12387,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="18.75" customHeight="1">
+    <row r="301" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -12418,7 +12422,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="18.75" customHeight="1">
+    <row r="302" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -12453,7 +12457,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="18.75" customHeight="1">
+    <row r="303" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -12488,7 +12492,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="18.75" customHeight="1">
+    <row r="304" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -12523,7 +12527,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="18.75" customHeight="1">
+    <row r="305" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -12558,7 +12562,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="18.75" customHeight="1">
+    <row r="306" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -12593,7 +12597,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="18.75" customHeight="1">
+    <row r="307" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -12628,7 +12632,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="18.75" customHeight="1">
+    <row r="308" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -12663,7 +12667,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="18.75" customHeight="1">
+    <row r="309" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -12698,7 +12702,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="15">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -12706,7 +12710,7 @@
         <v>653</v>
       </c>
       <c r="C310" t="s">
-        <v>683</v>
+        <v>26</v>
       </c>
       <c r="D310" t="s">
         <v>670</v>
@@ -12715,7 +12719,7 @@
         <v>673</v>
       </c>
       <c r="F310" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="G310" s="7">
         <v>45643</v>
@@ -12730,7 +12734,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="15">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -12738,7 +12742,7 @@
         <v>654</v>
       </c>
       <c r="C311" t="s">
-        <v>684</v>
+        <v>26</v>
       </c>
       <c r="D311" t="s">
         <v>671</v>
@@ -12762,7 +12766,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="15">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -12770,7 +12774,7 @@
         <v>655</v>
       </c>
       <c r="C312" t="s">
-        <v>685</v>
+        <v>26</v>
       </c>
       <c r="D312" t="s">
         <v>671</v>
@@ -12794,7 +12798,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="15">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -12802,7 +12806,7 @@
         <v>658</v>
       </c>
       <c r="C313" t="s">
-        <v>686</v>
+        <v>26</v>
       </c>
       <c r="D313" t="s">
         <v>670</v>
@@ -12811,7 +12815,7 @@
         <v>673</v>
       </c>
       <c r="F313" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="G313" s="7">
         <v>45643</v>
@@ -12826,7 +12830,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="15">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -12834,7 +12838,7 @@
         <v>659</v>
       </c>
       <c r="C314" t="s">
-        <v>687</v>
+        <v>26</v>
       </c>
       <c r="D314" t="s">
         <v>678</v>
@@ -12843,7 +12847,7 @@
         <v>675</v>
       </c>
       <c r="F314" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G314" s="7">
         <v>45644</v>
@@ -12858,7 +12862,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="15">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -12866,7 +12870,7 @@
         <v>660</v>
       </c>
       <c r="C315" t="s">
-        <v>688</v>
+        <v>26</v>
       </c>
       <c r="D315" t="s">
         <v>679</v>
@@ -12890,7 +12894,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="15">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -12898,7 +12902,7 @@
         <v>661</v>
       </c>
       <c r="C316" t="s">
-        <v>689</v>
+        <v>26</v>
       </c>
       <c r="D316" t="s">
         <v>679</v>
@@ -12922,7 +12926,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="15">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -12930,7 +12934,7 @@
         <v>662</v>
       </c>
       <c r="C317" t="s">
-        <v>690</v>
+        <v>26</v>
       </c>
       <c r="D317" t="s">
         <v>678</v>
@@ -12939,7 +12943,7 @@
         <v>675</v>
       </c>
       <c r="F317" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G317" s="7">
         <v>45644</v>
@@ -12954,7 +12958,7 @@
         <v>315.228571428571</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="15">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -12962,7 +12966,7 @@
         <v>663</v>
       </c>
       <c r="C318" t="s">
-        <v>691</v>
+        <v>26</v>
       </c>
       <c r="D318" t="s">
         <v>680</v>
@@ -12986,7 +12990,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="15">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -12994,7 +12998,7 @@
         <v>664</v>
       </c>
       <c r="C319" t="s">
-        <v>692</v>
+        <v>26</v>
       </c>
       <c r="D319" t="s">
         <v>682</v>
@@ -13003,7 +13007,7 @@
         <v>669</v>
       </c>
       <c r="F319" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="G319" s="7">
         <v>45646</v>
@@ -13018,7 +13022,7 @@
         <v>316.88571428571402</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="15">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -13026,7 +13030,7 @@
         <v>665</v>
       </c>
       <c r="C320" t="s">
-        <v>693</v>
+        <v>26</v>
       </c>
       <c r="D320" t="s">
         <v>680</v>
@@ -13050,7 +13054,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="15">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -13058,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="C321" t="s">
-        <v>694</v>
+        <v>26</v>
       </c>
       <c r="D321" t="s">
         <v>681</v>
@@ -13067,7 +13071,7 @@
         <v>668</v>
       </c>
       <c r="F321" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="G321" s="7">
         <v>45646</v>
@@ -13082,7 +13086,7 @@
         <v>318.54285714285697</v>
       </c>
     </row>
-    <row r="322" spans="1:10" ht="15">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -13090,7 +13094,7 @@
         <v>666</v>
       </c>
       <c r="C322" t="s">
-        <v>695</v>
+        <v>26</v>
       </c>
       <c r="D322" t="s">
         <v>682</v>
@@ -13099,7 +13103,7 @@
         <v>668</v>
       </c>
       <c r="F322" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="G322" s="7">
         <v>45646</v>
@@ -13114,7 +13118,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="15">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -13122,7 +13126,7 @@
         <v>657</v>
       </c>
       <c r="C323" t="s">
-        <v>696</v>
+        <v>26</v>
       </c>
       <c r="D323" t="s">
         <v>680</v>
@@ -13146,68 +13150,196 @@
         <v>321</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="15">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A324" s="4">
         <v>323</v>
       </c>
       <c r="B324" t="s">
+        <v>689</v>
+      </c>
+      <c r="C324" t="s">
+        <v>690</v>
+      </c>
+      <c r="D324" t="s">
+        <v>692</v>
+      </c>
+      <c r="E324" t="s">
+        <v>691</v>
+      </c>
+      <c r="F324" t="s">
+        <v>693</v>
+      </c>
+      <c r="G324" t="s">
+        <v>694</v>
+      </c>
+      <c r="H324" t="s">
+        <v>695</v>
+      </c>
+      <c r="I324" t="s">
         <v>700</v>
-      </c>
-      <c r="C324" t="s">
-        <v>701</v>
-      </c>
-      <c r="D324" t="s">
-        <v>703</v>
-      </c>
-      <c r="E324" t="s">
-        <v>702</v>
-      </c>
-      <c r="F324" t="s">
-        <v>704</v>
-      </c>
-      <c r="G324" t="s">
-        <v>705</v>
-      </c>
-      <c r="H324" t="s">
-        <v>706</v>
-      </c>
-      <c r="I324" t="s">
-        <v>711</v>
       </c>
       <c r="J324" s="4">
         <v>324</v>
       </c>
     </row>
-    <row r="325" spans="1:10" ht="15">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A325" s="4">
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="C325" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="D325" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="E325" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="F325" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="G325" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="H325" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="I325" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="J325" s="4">
         <v>323</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A326" s="4">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
+        <v>701</v>
+      </c>
+      <c r="C326" t="s">
+        <v>705</v>
+      </c>
+      <c r="D326" t="s">
+        <v>671</v>
+      </c>
+      <c r="E326" t="s">
+        <v>674</v>
+      </c>
+      <c r="F326" t="s">
+        <v>687</v>
+      </c>
+      <c r="G326" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H326" t="s">
+        <v>683</v>
+      </c>
+      <c r="I326" t="s">
+        <v>709</v>
+      </c>
+      <c r="J326" s="4">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A327" s="4">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
+        <v>702</v>
+      </c>
+      <c r="C327" t="s">
+        <v>706</v>
+      </c>
+      <c r="D327" t="s">
+        <v>670</v>
+      </c>
+      <c r="E327" t="s">
+        <v>673</v>
+      </c>
+      <c r="F327" t="s">
+        <v>687</v>
+      </c>
+      <c r="G327" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H327" t="s">
+        <v>683</v>
+      </c>
+      <c r="I327" t="s">
+        <v>709</v>
+      </c>
+      <c r="J327" s="4">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A328" s="4">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
+        <v>703</v>
+      </c>
+      <c r="C328" t="s">
+        <v>707</v>
+      </c>
+      <c r="D328" t="s">
+        <v>671</v>
+      </c>
+      <c r="E328" t="s">
+        <v>674</v>
+      </c>
+      <c r="F328" t="s">
+        <v>687</v>
+      </c>
+      <c r="G328" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H328" t="s">
+        <v>684</v>
+      </c>
+      <c r="I328" t="s">
+        <v>710</v>
+      </c>
+      <c r="J328" s="4">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A329" s="4">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
+        <v>704</v>
+      </c>
+      <c r="C329" t="s">
+        <v>708</v>
+      </c>
+      <c r="D329" t="s">
+        <v>670</v>
+      </c>
+      <c r="E329" t="s">
+        <v>673</v>
+      </c>
+      <c r="F329" t="s">
+        <v>687</v>
+      </c>
+      <c r="G329" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H329" t="s">
+        <v>685</v>
+      </c>
+      <c r="I329" t="s">
+        <v>711</v>
+      </c>
+      <c r="J329" s="4">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/data_management2026/database_entry.xlsx
+++ b/data_management2026/database_entry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tippi\SynologyDrive\Tsing_Hua\third_grade\project\RealTimeAccompaniment_COPY\data_management2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856A94D4-D7E0-4E24-90DE-16677F8E4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E082212F-23A2-419D-AC9E-C89C240E6BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="4515" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="722">
   <si>
     <t>entry</t>
   </si>
@@ -2201,6 +2201,39 @@
   </si>
   <si>
     <t>data_management2026\py_scripts_and_notes\extract_interpretation_6hands.py</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_1_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\interpretation_Take_1_Human_2.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputinterpretation_Take_3_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputinterpretation_Take_3_Human_2.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_3_Human_1.txt</t>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241217\inputmslog_Take_1_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_1piano.py</t>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_2piano.py</t>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_3piano.py</t>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_4piano.py</t>
   </si>
 </sst>
 </file>
@@ -2610,7 +2643,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K329"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
@@ -13342,6 +13375,134 @@
         <v>327</v>
       </c>
     </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A330" s="4">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
+        <v>712</v>
+      </c>
+      <c r="C330" t="s">
+        <v>717</v>
+      </c>
+      <c r="D330" t="s">
+        <v>670</v>
+      </c>
+      <c r="E330" t="s">
+        <v>673</v>
+      </c>
+      <c r="F330" t="s">
+        <v>687</v>
+      </c>
+      <c r="G330" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H330" t="s">
+        <v>683</v>
+      </c>
+      <c r="I330" t="s">
+        <v>718</v>
+      </c>
+      <c r="J330" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A331" s="4">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
+        <v>713</v>
+      </c>
+      <c r="C331" t="s">
+        <v>717</v>
+      </c>
+      <c r="D331" t="s">
+        <v>671</v>
+      </c>
+      <c r="E331" t="s">
+        <v>674</v>
+      </c>
+      <c r="F331" t="s">
+        <v>687</v>
+      </c>
+      <c r="G331" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H331" t="s">
+        <v>683</v>
+      </c>
+      <c r="I331" t="s">
+        <v>719</v>
+      </c>
+      <c r="J331" s="5">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A332" s="4">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
+        <v>714</v>
+      </c>
+      <c r="C332" t="s">
+        <v>716</v>
+      </c>
+      <c r="D332" t="s">
+        <v>670</v>
+      </c>
+      <c r="E332" t="s">
+        <v>673</v>
+      </c>
+      <c r="F332" t="s">
+        <v>687</v>
+      </c>
+      <c r="G332" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H332" t="s">
+        <v>684</v>
+      </c>
+      <c r="I332" t="s">
+        <v>720</v>
+      </c>
+      <c r="J332" s="5">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A333" s="4">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>715</v>
+      </c>
+      <c r="C333" t="s">
+        <v>716</v>
+      </c>
+      <c r="D333" t="s">
+        <v>671</v>
+      </c>
+      <c r="E333" t="s">
+        <v>674</v>
+      </c>
+      <c r="F333" t="s">
+        <v>687</v>
+      </c>
+      <c r="G333" s="7">
+        <v>45643</v>
+      </c>
+      <c r="H333" t="s">
+        <v>685</v>
+      </c>
+      <c r="I333" t="s">
+        <v>721</v>
+      </c>
+      <c r="J333" s="5">
+        <v>331</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data_management2026/database_entry.xlsx
+++ b/data_management2026/database_entry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tippi\SynologyDrive\Tsing_Hua\third_grade\project\RealTimeAccompaniment_COPY\data_management2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E082212F-23A2-419D-AC9E-C89C240E6BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96803A72-2CFC-4989-8FF3-A88934BA169F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2783" uniqueCount="720">
   <si>
     <t>entry</t>
   </si>
@@ -2064,25 +2064,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>logs\faure1\outputscore.txt</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>logs\faure2\outputscore.txt</t>
-  </si>
-  <si>
-    <t>logs\faure2\outputscore.txt</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>faure1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>faure2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>debussy3_2</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2197,12 +2178,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>data_management2026\py_scripts_and_notes\extract_interpretation_5hands.py</t>
-  </si>
-  <si>
-    <t>data_management2026\py_scripts_and_notes\extract_interpretation_6hands.py</t>
-  </si>
-  <si>
     <t>data_management2026\202412 Experiments\20241217\interpretation_Take_1_Human_1.txt</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2227,13 +2202,34 @@
     <t>data_management2026\py_scripts_and_notes\extract_interpretation_1piano.py</t>
   </si>
   <si>
-    <t>data_management2026\py_scripts_and_notes\extract_interpretation_2piano.py</t>
-  </si>
-  <si>
-    <t>data_management2026\py_scripts_and_notes\extract_interpretation_3piano.py</t>
-  </si>
-  <si>
-    <t>data_management2026\py_scripts_and_notes\extract_interpretation_4piano.py</t>
+    <t>faure5_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>faure5_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>logs\faure5_1\outputscore.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>logs\faure5_2\outputscore.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241218\inputinterpretation_Take_6_Human_1.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241218\inputinterpretation_Take_6_Human_2.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\202412 Experiments\20241218\inputmslog_Take_6_Human_1.txt</t>
+  </si>
+  <si>
+    <t>202412 Experiments\20241218\asdf Edit 1.tracktionedit</t>
   </si>
 </sst>
 </file>
@@ -2643,7 +2639,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K333"/>
+  <dimension ref="A1:K337"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
@@ -12752,7 +12748,7 @@
         <v>673</v>
       </c>
       <c r="F310" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G310" s="7">
         <v>45643</v>
@@ -12848,7 +12844,7 @@
         <v>673</v>
       </c>
       <c r="F313" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G313" s="7">
         <v>45643</v>
@@ -12874,13 +12870,13 @@
         <v>26</v>
       </c>
       <c r="D314" t="s">
-        <v>678</v>
+        <v>712</v>
       </c>
       <c r="E314" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="F314" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G314" s="7">
         <v>45644</v>
@@ -12906,10 +12902,10 @@
         <v>26</v>
       </c>
       <c r="D315" t="s">
-        <v>679</v>
+        <v>713</v>
       </c>
       <c r="E315" t="s">
-        <v>676</v>
+        <v>715</v>
       </c>
       <c r="F315" t="s">
         <v>515</v>
@@ -12938,10 +12934,10 @@
         <v>26</v>
       </c>
       <c r="D316" t="s">
-        <v>679</v>
+        <v>713</v>
       </c>
       <c r="E316" t="s">
-        <v>677</v>
+        <v>715</v>
       </c>
       <c r="F316" t="s">
         <v>515</v>
@@ -12970,13 +12966,13 @@
         <v>26</v>
       </c>
       <c r="D317" t="s">
-        <v>678</v>
+        <v>712</v>
       </c>
       <c r="E317" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="F317" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G317" s="7">
         <v>45644</v>
@@ -13002,7 +12998,7 @@
         <v>26</v>
       </c>
       <c r="D318" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E318" t="s">
         <v>667</v>
@@ -13034,13 +13030,13 @@
         <v>26</v>
       </c>
       <c r="D319" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="E319" t="s">
         <v>669</v>
       </c>
       <c r="F319" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G319" s="7">
         <v>45646</v>
@@ -13066,7 +13062,7 @@
         <v>26</v>
       </c>
       <c r="D320" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E320" t="s">
         <v>667</v>
@@ -13098,13 +13094,13 @@
         <v>26</v>
       </c>
       <c r="D321" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="E321" t="s">
         <v>668</v>
       </c>
       <c r="F321" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G321" s="7">
         <v>45646</v>
@@ -13130,13 +13126,13 @@
         <v>26</v>
       </c>
       <c r="D322" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="E322" t="s">
         <v>668</v>
       </c>
       <c r="F322" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G322" s="7">
         <v>45646</v>
@@ -13162,7 +13158,7 @@
         <v>26</v>
       </c>
       <c r="D323" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E323" t="s">
         <v>667</v>
@@ -13188,28 +13184,28 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
+        <v>684</v>
+      </c>
+      <c r="C324" t="s">
+        <v>685</v>
+      </c>
+      <c r="D324" t="s">
+        <v>687</v>
+      </c>
+      <c r="E324" t="s">
+        <v>686</v>
+      </c>
+      <c r="F324" t="s">
+        <v>688</v>
+      </c>
+      <c r="G324" t="s">
         <v>689</v>
       </c>
-      <c r="C324" t="s">
+      <c r="H324" t="s">
         <v>690</v>
       </c>
-      <c r="D324" t="s">
-        <v>692</v>
-      </c>
-      <c r="E324" t="s">
-        <v>691</v>
-      </c>
-      <c r="F324" t="s">
-        <v>693</v>
-      </c>
-      <c r="G324" t="s">
-        <v>694</v>
-      </c>
-      <c r="H324" t="s">
+      <c r="I324" t="s">
         <v>695</v>
-      </c>
-      <c r="I324" t="s">
-        <v>700</v>
       </c>
       <c r="J324" s="4">
         <v>324</v>
@@ -13220,28 +13216,28 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C325" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D325" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="E325" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="F325" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G325" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="H325" t="s">
+        <v>690</v>
+      </c>
+      <c r="I325" t="s">
         <v>695</v>
-      </c>
-      <c r="I325" t="s">
-        <v>700</v>
       </c>
       <c r="J325" s="4">
         <v>323</v>
@@ -13252,10 +13248,10 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C326" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D326" t="s">
         <v>671</v>
@@ -13264,16 +13260,16 @@
         <v>674</v>
       </c>
       <c r="F326" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G326" s="7">
         <v>45643</v>
       </c>
       <c r="H326" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I326" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="J326" s="4">
         <v>326</v>
@@ -13284,10 +13280,10 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C327" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D327" t="s">
         <v>670</v>
@@ -13296,16 +13292,16 @@
         <v>673</v>
       </c>
       <c r="F327" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G327" s="7">
         <v>45643</v>
       </c>
       <c r="H327" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I327" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="J327" s="4">
         <v>325</v>
@@ -13316,10 +13312,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C328" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="D328" t="s">
         <v>671</v>
@@ -13328,16 +13324,16 @@
         <v>674</v>
       </c>
       <c r="F328" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G328" s="7">
         <v>45643</v>
       </c>
       <c r="H328" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="I328" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="J328" s="4">
         <v>328</v>
@@ -13348,10 +13344,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C329" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D329" t="s">
         <v>670</v>
@@ -13360,16 +13356,16 @@
         <v>673</v>
       </c>
       <c r="F329" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G329" s="7">
         <v>45643</v>
       </c>
       <c r="H329" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I329" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="J329" s="4">
         <v>327</v>
@@ -13380,10 +13376,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C330" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D330" t="s">
         <v>670</v>
@@ -13392,16 +13388,16 @@
         <v>673</v>
       </c>
       <c r="F330" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G330" s="7">
         <v>45643</v>
       </c>
       <c r="H330" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I330" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="J330" s="5">
         <v>330</v>
@@ -13412,10 +13408,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C331" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D331" t="s">
         <v>671</v>
@@ -13424,16 +13420,16 @@
         <v>674</v>
       </c>
       <c r="F331" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G331" s="7">
         <v>45643</v>
       </c>
       <c r="H331" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I331" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="J331" s="5">
         <v>329</v>
@@ -13444,10 +13440,10 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C332" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D332" t="s">
         <v>670</v>
@@ -13456,16 +13452,16 @@
         <v>673</v>
       </c>
       <c r="F332" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G332" s="7">
         <v>45643</v>
       </c>
       <c r="H332" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="I332" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="J332" s="5">
         <v>332</v>
@@ -13476,10 +13472,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C333" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D333" t="s">
         <v>671</v>
@@ -13488,20 +13484,90 @@
         <v>674</v>
       </c>
       <c r="F333" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G333" s="7">
         <v>45643</v>
       </c>
       <c r="H333" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I333" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="J333" s="5">
         <v>331</v>
       </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A334" s="4">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
+        <v>716</v>
+      </c>
+      <c r="C334" t="s">
+        <v>718</v>
+      </c>
+      <c r="D334" t="s">
+        <v>712</v>
+      </c>
+      <c r="E334" t="s">
+        <v>714</v>
+      </c>
+      <c r="F334" t="s">
+        <v>681</v>
+      </c>
+      <c r="G334" s="7">
+        <v>45644</v>
+      </c>
+      <c r="H334" t="s">
+        <v>719</v>
+      </c>
+      <c r="I334" t="s">
+        <v>711</v>
+      </c>
+      <c r="J334" s="5">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A335" s="4">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
+        <v>717</v>
+      </c>
+      <c r="C335" t="s">
+        <v>718</v>
+      </c>
+      <c r="D335" t="s">
+        <v>713</v>
+      </c>
+      <c r="E335" t="s">
+        <v>715</v>
+      </c>
+      <c r="F335" t="s">
+        <v>681</v>
+      </c>
+      <c r="G335" s="7">
+        <v>45644</v>
+      </c>
+      <c r="H335" t="s">
+        <v>719</v>
+      </c>
+      <c r="I335" t="s">
+        <v>711</v>
+      </c>
+      <c r="J335" s="5">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G336" s="7"/>
+    </row>
+    <row r="337" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G337" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
